--- a/Data/Home/LivingRoom.Humidity.xlsx
+++ b/Data/Home/LivingRoom.Humidity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709279409</v>
+        <v>1712136953</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709283488</v>
+        <v>1712141538</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709277977</v>
+        <v>1712457340</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709285490</v>
+        <v>1712460516</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709313810</v>
+        <v>1712551192</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709319159</v>
+        <v>1712552099</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +667,15 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709369105</v>
+        <v>1712556396</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709426717</v>
+        <v>1712557429</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +737,15 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +764,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709437436</v>
+        <v>1712565707</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +778,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +797,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709443222</v>
+        <v>1712623252</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +811,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709449299</v>
+        <v>1712628158</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +844,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709609864</v>
+        <v>1712651854</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +877,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709622551</v>
+        <v>1713161009</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +906,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709690775</v>
+        <v>1713165711</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +939,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +962,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709697091</v>
+        <v>1713168403</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +972,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +995,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709714824</v>
+        <v>1713181367</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1005,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1028,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709746623</v>
+        <v>1713191079</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1038,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1061,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709749368</v>
+        <v>1713225614</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1071,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1094,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709758267</v>
+        <v>1713245104</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1104,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1127,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709760726</v>
+        <v>1713247798</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1137,15 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1164,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709771246</v>
+        <v>1713248040</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1174,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1197,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709779449</v>
+        <v>1713248363</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1207,11 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1230,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709783520</v>
+        <v>1713249041</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1244,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1263,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709791136</v>
+        <v>1713255116</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1273,11 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1296,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709797954</v>
+        <v>1713255779</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1310,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1329,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709800178</v>
+        <v>1713262612</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1343,11 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1366,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709856829</v>
+        <v>1713266474</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1380,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1399,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709869519</v>
+        <v>1713339270</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1409,11 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1432,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709871881</v>
+        <v>1713340615</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1442,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1465,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709882549</v>
+        <v>1713344083</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1475,15 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1502,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709886686</v>
+        <v>1713344345</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1512,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1535,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710043227</v>
+        <v>1713344669</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1549,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1568,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710053420</v>
+        <v>1713345274</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1582,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1601,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710332469</v>
+        <v>1713349717</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1615,11 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1638,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710346067</v>
+        <v>1713357037</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1652,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1671,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710579389</v>
+        <v>1713357929</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1685,11 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1708,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710637005</v>
+        <v>1713429844</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1722,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1741,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710655975</v>
+        <v>1713430722</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1755,11 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1778,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710669882</v>
+        <v>1713436824</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1792,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1811,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710721457</v>
+        <v>1713489773</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1821,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1844,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710738037</v>
+        <v>1713513749</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1777,10 +1854,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1877,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710748461</v>
+        <v>1713516653</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1887,15 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1914,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710758189</v>
+        <v>1713516895</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1924,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1947,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710780024</v>
+        <v>1713517222</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1957,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1980,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710818405</v>
+        <v>1713517865</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1994,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2013,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710889016</v>
+        <v>1713523801</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2023,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2046,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710893119</v>
+        <v>1713624454</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2056,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2079,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710924665</v>
+        <v>1713633806</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2089,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2112,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710931287</v>
+        <v>1713630635</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2033,10 +2122,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2145,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710978446</v>
+        <v>1713660495</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2155,11 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2178,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710982552</v>
+        <v>1713664008</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2188,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2211,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1711006948</v>
+        <v>1713671949</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2221,15 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2248,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1711014123</v>
+        <v>1713672210</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2161,10 +2258,11 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2281,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1711082891</v>
+        <v>1713672555</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2295,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2314,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1711090363</v>
+        <v>1713673303</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2328,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2347,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1711363266</v>
+        <v>1713675820</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2257,10 +2357,11 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2380,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1711366340</v>
+        <v>1713676565</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2394,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2413,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1711438659</v>
+        <v>1713680587</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2446,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1711445982</v>
+        <v>1713681301</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2460,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2479,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1711458516</v>
+        <v>1713685249</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2489,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2512,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1711465425</v>
+        <v>1713686395</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2522,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2545,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1711545333</v>
+        <v>1713690018</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2555,15 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2582,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1711555218</v>
+        <v>1713690255</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2481,10 +2592,11 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: Moist</t>
+          <t>LivingRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2615,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1711563272</v>
+        <v>1713690587</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2625,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2648,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1711557173</v>
+        <v>1713691200</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2662,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2681,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1711629078</v>
+        <v>1713695558</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2695,11 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2718,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1711635558</v>
+        <v>1713696304</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2732,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2751,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1711636972</v>
+        <v>1713701581</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2765,1627 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1713702296</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1713704870</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1713708542</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1713716408</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1713718746</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1713743458</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1713746042</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1713752535</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ExtremelyDry</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1713752778</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1713753101</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1713753808</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1713759875</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1713760537</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1713767845</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1713769142</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1713772754</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ExtremelyDry</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1713773010</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1713773347</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1713774016</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1713775161</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1713781128</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1713782014</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1713833473</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1713834309</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1713850748</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1713855116</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1713855825</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1713863877</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1713866181</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1713868287</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1713917123</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1713921829</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1713935890</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1713938281</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ExtremelyDry</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1713938517</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Dry</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1713938842</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1713939535</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1713945416</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1713946066</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1713947096</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ExcessivelyHumid</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1713952613</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1714025578</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1714026886</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1714036961</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1714047457</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1714180906</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1714185812</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1714195572</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>LivingRoom.Humidity.state: ComfortableHumidity</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
